--- a/data/HSK_KouYu_Sheet_mau.xlsx
+++ b/data/HSK_KouYu_Sheet_mau.xlsx
@@ -23,7 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Submissions" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attempts" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AiPrompts" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attempts" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -830,28 +831,62 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>AiPrompts</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>new_password</t>
+          <t>prompt</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gõ mật khẩu mới rồi chạy menu HSK 口语 → Băm mật khẩu mới. Ô này sẽ được xoá sau khi băm.</t>
+          <t>Prompt gửi cho Gemini khi bấm Phân tích. Dòng _chung là chỉ dẫn chung; các dòng còn lại theo phần luyện. Chỉ sửa câu chữ, giữ nguyên các biến {{…}}. Xoá hoặc ẩn dòng thì dùng prompt mặc định trong mã.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ai_limit</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Số lượt AI phân tích mỗi ngày của người này. Để trống = theo Config → ai_daily_limit; 0 = không cho dùng AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>new_password</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Gõ mật khẩu mới rồi chạy menu HSK 口语 → Băm mật khẩu mới. Ô này sẽ được xoá sau khi băm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Sessions / Submissions / Attempts</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Do ứng dụng tự ghi. Có thể xem, lọc, nhưng không nên sửa tay.</t>
         </is>
@@ -2643,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2800,6 +2835,70 @@
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Tài liệu: số giây nói cho mỗi câu hỏi phụ nếu tài liệu để trống</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ai_enabled</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Bật/tắt nút Phân tích bằng AI cho mọi người (cần đặt Gemini API key qua menu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ai_models</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>gemini-flash-latest</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Tên model Gemini, thử lần lượt từ trái sang phải, ngăn bằng dấu phẩy. Xem tên model hiện hành trong Google AI Studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ai_daily_limit</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Số lượt phân tích mỗi người mỗi ngày (cột ai_limit trong Users ghi đè cho từng người; 0 = không dùng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ai_max_sec</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ghi âm dài nhất (giây) cho một lượt phân tích</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2823,9 +2922,10 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2861,15 +2961,20 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>ai_limit</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>last_login</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2900,9 +3005,10 @@
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Đổi mật khẩu ở cột new_password rồi chạy menu Băm mật khẩu mới</t>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu ở cột new_password rồi chạy menu Băm mật khẩu mới. ai_limit trống = theo Config</t>
         </is>
       </c>
     </row>
@@ -2964,7 +3070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2980,11 +3086,13 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3055,25 +3163,35 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
+          <t>ai_scores</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>ai_feedback</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
           <t>checklist_done</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>checklist_total</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>checklist_missed</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -3085,6 +3203,213 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>_chung</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bạn là giám khảo khẩu ngữ tiếng Trung trình độ HSK 7–9 (tham khảo cách chấm IELTS Speaking) và là giáo viên dạy tiếng Trung cho người Việt. Bạn nhận một file ghi âm người học nói tiếng Trung.
+Quy tắc bắt buộc:
+1. transcript: chép bằng chữ Hán giản thể đúng những gì nghe được, kể cả câu sai ngữ pháp, từ lặp, từ đệm (然后、那个…). Không sửa, không thêm ý. Chỗ không nghe rõ ghi [?].
+2. Nếu bản ghi im lặng, quá ngắn hoặc không phải tiếng Trung: transcript để trống, mọi điểm bằng 0, summary giải thích ngắn.
+3. Chấm mỗi tiêu chí từ 1 đến 5 theo thang bên dưới (được dùng 2 và 4). Phát âm (pro) chấm dựa trên âm thanh thực tế, không dựa trên văn bản.
+4. pronunciation: tối đa 8 chỗ sai thanh điệu hoặc sai âm: chữ Hán, pinyin đúng, âm nghe được.
+5. errors: tối đa 8 lỗi từ vựng, ngữ pháp hoặc diễn đạt: câu gốc (trích từ transcript), câu sửa, lý do ngắn.
+6. improved: viết lại bài nói ở mức 5/5, giữ ý và ví dụ của người học, độ dài phù hợp với {{sec}} giây nói.
+7. summary, comments, why, extra viết bằng tiếng Việt, ngắn gọn, cụ thể; câu tiếng Trung giữ nguyên chữ Hán.
+Thang chấm:
+{{rubric}}</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ dẫn chung gửi kèm mọi lần phân tích. {{rubric}} = thang chấm lấy từ tab Rubric; {{sec}} = số giây đã nói.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Phần luyện: Phản xạ nhanh (kiểu IELTS Part 1), trả lời khoảng 30 giây.
+Câu hỏi: {{question}}
+Trong extra: câu đầu có trả lời thẳng câu hỏi không; có lý do hoặc ví dụ cụ thể không.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Phản xạ nhanh. Biến: {{question}}</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Phần luyện: HSK 7–9, nói dựa trên tài liệu.
+Tài liệu:
+{{material}}
+Nhiệm vụ hoặc câu hỏi: {{question}}
+Câu trả lời tham khảo (chỉ để đối chiếu, không bắt buộc giống): {{sample}}
+Trong extra: người học có thuật lại đủ ý chính và đúng thông tin của tài liệu không; liệt kê ý bị sót hoặc sai.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tài liệu. Biến: {{material}}, {{question}}, {{sample}}</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>opinion</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Phần luyện: HSK 7–9 phần nêu quan điểm, kết hợp câu hỏi xoáy kiểu IELTS Part 3.
+Câu hỏi chính của đề: {{main}}
+Câu hỏi đang trả lời: {{question}}
+Trong extra: lập trường có rõ không; có lý do, ví dụ, nhượng bộ không; nếu là câu hỏi xoáy thì có trả lời đúng trọng tâm không.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Quan điểm. Biến: {{main}} (câu hỏi chính), {{question}} (câu đang trả lời)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>interp</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Phần luyện: dịch nói Việt → Trung.
+Đoạn tiếng Việt:
+{{source_vi}}
+Bản dịch tham khảo (một cách dịch, không phải duy nhất): {{reference}}
+Thuật ngữ cần có: {{terms}}
+Trong extra: liệt kê ý bị dịch sót hoặc sai nghĩa và thuật ngữ dịch sai. improved: bản dịch nói tự nhiên dựa trên ý người học.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Dịch nói. Biến: {{source_vi}}, {{reference}}, {{terms}}</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Phần luyện: đọc kịch bản video ngắn cho 抖音 / 小红书 (loại: {{type}}), thời lượng mục tiêu {{target_sec}} giây.
+Kịch bản người học định đọc:
+{{script}}
+Trong extra: so lời đọc với kịch bản (chỗ vấp, đọc sai, bỏ câu); nhận xét tốc độ, nhấn nhá và năng lượng giọng khi nói trước ống kính. Chấm cả các tiêu chí riêng cho video. improved: chỉnh kịch bản cho dễ nói hơn, giữ nguyên ý.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Video. Biến: {{type}}, {{script}}, {{target_sec}}</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"có,không"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
